--- a/artfynd/A 20776-2024 artfynd.xlsx
+++ b/artfynd/A 20776-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>66507105</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592342.8869837666</v>
+        <v>592343</v>
       </c>
       <c r="R2" t="n">
-        <v>6982266.324561661</v>
+        <v>6982266</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2013-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66507109</v>
+        <v>66507108</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Abborrtjärnbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592342.8869837666</v>
+        <v>592343</v>
       </c>
       <c r="R3" t="n">
-        <v>6982266.324561661</v>
+        <v>6982266</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +845,9 @@
           <t>2013-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66507108</v>
+        <v>66507109</v>
       </c>
       <c r="B4" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,34 +890,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>990</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Abborrtjärnbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592342.8869837666</v>
+        <v>592343</v>
       </c>
       <c r="R4" t="n">
-        <v>6982266.324561661</v>
+        <v>6982266</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +951,9 @@
           <t>2013-09-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +967,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 20776-2024 artfynd.xlsx
+++ b/artfynd/A 20776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66507105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66507108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66507109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>